--- a/26-2 Sports Day/26-2 Sports Day 기획 일정.xlsx
+++ b/26-2 Sports Day/26-2 Sports Day 기획 일정.xlsx
@@ -272,7 +272,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -304,13 +304,13 @@
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -333,46 +333,49 @@
     <xf borderId="1" fillId="8" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="7" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="2" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="9" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="9" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="5" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="10" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="1" fillId="3" fontId="5" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="5" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf borderId="1" fillId="11" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="4" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1151,14 +1154,14 @@
         <v>19</v>
       </c>
       <c r="C16" s="17"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="25" t="s">
+      <c r="D16" s="25"/>
+      <c r="E16" s="26" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="26" t="s">
+      <c r="F16" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="G16" s="27"/>
+      <c r="G16" s="28"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
@@ -1180,19 +1183,19 @@
       <c r="Z16" s="2"/>
     </row>
     <row r="17">
-      <c r="A17" s="28"/>
-      <c r="B17" s="29" t="s">
+      <c r="A17" s="29"/>
+      <c r="B17" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="30" t="s">
+      <c r="C17" s="29"/>
+      <c r="D17" s="29"/>
+      <c r="E17" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="F17" s="30" t="s">
+      <c r="F17" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="G17" s="28"/>
+      <c r="G17" s="29"/>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
@@ -1214,25 +1217,25 @@
       <c r="Z17" s="2"/>
     </row>
     <row r="18">
-      <c r="A18" s="31">
+      <c r="A18" s="32">
         <v>46271.0</v>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="32">
         <v>46272.0</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="32">
         <v>46273.0</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="32">
         <v>46274.0</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="32">
         <v>46275.0</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="32">
         <v>46276.0</v>
       </c>
-      <c r="G18" s="31">
+      <c r="G18" s="32">
         <v>46277.0</v>
       </c>
       <c r="H18" s="2"/>
@@ -1261,11 +1264,11 @@
         <v>25</v>
       </c>
       <c r="C19" s="7"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="33" t="s">
+      <c r="D19" s="33"/>
+      <c r="E19" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="34" t="s">
+      <c r="F19" s="35" t="s">
         <v>27</v>
       </c>
       <c r="G19" s="7"/>
@@ -1332,17 +1335,17 @@
       <c r="Z20" s="2"/>
     </row>
     <row r="21">
-      <c r="A21" s="27"/>
+      <c r="A21" s="28"/>
       <c r="B21" s="10"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="35" t="s">
+      <c r="F21" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="G21" s="33" t="s">
+      <c r="G21" s="34" t="s">
         <v>30</v>
       </c>
       <c r="H21" s="2"/>
@@ -1394,7 +1397,7 @@
       <c r="Z22" s="2"/>
     </row>
     <row r="23">
-      <c r="A23" s="36" t="s">
+      <c r="A23" s="37" t="s">
         <v>31</v>
       </c>
       <c r="B23" s="2"/>
@@ -28951,7 +28954,7 @@
   <mergeCells count="3">
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="F14:G14"/>
-    <mergeCell ref="B16:D16"/>
+    <mergeCell ref="B16:C16"/>
   </mergeCells>
   <drawing r:id="rId1"/>
 </worksheet>
